--- a/data/douras/excel/802576637_2025_invoices.xlsx
+++ b/data/douras/excel/802576637_2025_invoices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,182 +543,186 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>400011219241353</t>
+          <t>400011186892779</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>094386010</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>094439854</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8Μ0ΤΔΑ</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ΑΠΟΔΕΙΞΗ</t>
+          <t>Τιμολόγιο Πώλησης</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>48,39</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11,61</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>60,00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>8970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>400011219241354</t>
+          <t>400011184830173</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>094386010</t>
+          <t>800916954</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TΔA</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>60038</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ΑΠΟΔΕΙΞΗ</t>
+          <t>Πιστωτικό Τιμολόγιο / Συσχετιζόμενο</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>-18,30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-4,39</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>-22,69</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>60038</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>400011185872109</t>
+          <t>400011219241355</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>094439854</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8Μ0ΤΔΑ</t>
-        </is>
-      </c>
+          <t>094386010</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Τιμολόγιο Πώλησης</t>
+          <t>ΑΠΟΔΕΙΞΗ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8,75</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2,10</t>
-        </is>
-      </c>
+          <t>9,4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>165</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>400011186892779</t>
+          <t>400009073184486</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>094439854</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
-        </is>
-      </c>
+          <t>800916954</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8Μ0ΤΔΑ</t>
+          <t>TΔA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -729,83 +733,87 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>48,39</t>
+          <t>129,99</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11,61</t>
+          <t>29,66</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>60,00</t>
+          <t>159,65</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>56096</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>400011184830173</t>
+          <t>400011213160102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>800916954</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>094439854</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TΔA</t>
+          <t>8Μ0ΤΔΑ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60038</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Πιστωτικό Τιμολόγιο / Συσχετιζόμενο</t>
+          <t>Τιμολόγιο Πώλησης</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-18,30</t>
+          <t>64,52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>15,48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-22,69</t>
+          <t>80,00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>60038</t>
+          <t>9036</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>400011219241355</t>
+          <t>400011219241356</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -814,7 +822,11 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ΑΛΠ</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>165</t>
@@ -843,168 +855,6 @@
         </is>
       </c>
       <c r="L8" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>400009073184486</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>800916954</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TΔA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>56096</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>10/04/2025</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Τιμολόγιο Πώλησης</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>129,99</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>29,66</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>159,65</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>56096</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>400011213160102</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>094439854</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ΤΡΑΚΑΔΑΣ Α.Ε.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8Μ0ΤΔΑ</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>9036</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>07/10/2025</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Τιμολόγιο Πώλησης</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>64,52</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15,48</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>80,00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>9036</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>400011219241356</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>094386010</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ΑΛΠ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>25/09/2025</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ΑΠΟΔΕΙΞΗ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>165</t>
         </is>
